--- a/bin/client.xlsx
+++ b/bin/client.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -568,15 +568,15 @@
       </c>
       <c r="F2" t="str">
         <f ca="1">IF(G2 &lt; 1, "A","B")</f>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G2">
         <f ca="1">RAND()*2</f>
-        <v>0.62785123748777072</v>
+        <v>1.6177930869317079</v>
       </c>
       <c r="H2" t="str">
         <f ca="1">CONCATENATE("(",B2,", ", CHAR(39), C2, CHAR(39), ", ", CHAR(39), D2, CHAR(39), ", ",  CHAR(39), TEXT(E2, "yyyy-mm-dd"), CHAR(39), ", ", CHAR(39), F2, CHAR(39), "),")</f>
-        <v>(1219, 'Kyle', 'Rowland', '2021-03-30', 'A'),</v>
+        <v>(1219, 'Kyle', 'Rowland', '2021-03-30', 'B'),</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -601,7 +601,7 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G26" ca="1" si="1">RAND()*2</f>
-        <v>1.0994949905925393</v>
+        <v>1.4619374004442318</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H26" ca="1" si="2">CONCATENATE("(",B3,", ", CHAR(39), C3, CHAR(39), ", ", CHAR(39), D3, CHAR(39), ", ",  CHAR(39), TEXT(E3, "yyyy-mm-dd"), CHAR(39), ", ", CHAR(39), F3, CHAR(39), "),")</f>
@@ -626,15 +626,15 @@
       </c>
       <c r="F4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G4">
         <f t="shared" ca="1" si="1"/>
-        <v>1.9465935508849479</v>
+        <v>0.79866803257932384</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1967, 'Agnes', 'Benton', '2021-04-23', 'B'),</v>
+        <v>(1967, 'Agnes', 'Benton', '2021-04-23', 'A'),</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -655,15 +655,15 @@
       </c>
       <c r="F5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G5">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31967764651435204</v>
+        <v>1.1716368964832831</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(195, 'Porter', 'Anthony', '2022-03-14', 'A'),</v>
+        <v>(195, 'Porter', 'Anthony', '2022-03-14', 'B'),</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -684,15 +684,15 @@
       </c>
       <c r="F6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G6">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3726288459621827</v>
+        <v>0.95692159029874713</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1407, 'Teddy', 'Hess', '2022-05-31', 'B'),</v>
+        <v>(1407, 'Teddy', 'Hess', '2022-05-31', 'A'),</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -717,7 +717,7 @@
       </c>
       <c r="G7">
         <f t="shared" ca="1" si="1"/>
-        <v>2.1503882852136558E-2</v>
+        <v>0.81062525384132145</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="G8">
         <f t="shared" ca="1" si="1"/>
-        <v>0.16366564556151753</v>
+        <v>7.6191103364802171E-3</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="G9">
         <f t="shared" ca="1" si="1"/>
-        <v>1.7668542635204536</v>
+        <v>1.9167135693985489</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -800,15 +800,15 @@
       </c>
       <c r="F10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G10">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5840253755262339</v>
+        <v>0.60900572730880165</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(466, 'Melanie', 'Sutton', '2023-05-05', 'B'),</v>
+        <v>(466, 'Melanie', 'Sutton', '2023-05-05', 'A'),</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -833,7 +833,7 @@
       </c>
       <c r="G11">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5024364467652742</v>
+        <v>1.5840189862847556</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="G12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7512549607096437</v>
+        <v>0.26171750989813103</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -887,15 +887,15 @@
       </c>
       <c r="F13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G13">
         <f t="shared" ca="1" si="1"/>
-        <v>1.9570308482998293</v>
+        <v>0.90111046261464933</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(212, 'Sean', 'Jimenez', '2023-08-17', 'B'),</v>
+        <v>(212, 'Sean', 'Jimenez', '2023-08-17', 'A'),</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -916,15 +916,15 @@
       </c>
       <c r="F14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G14">
         <f t="shared" ca="1" si="1"/>
-        <v>1.1101242439312604</v>
+        <v>0.46868941770079653</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(913, 'Celia', 'Cowan', '2023-09-08', 'B'),</v>
+        <v>(913, 'Celia', 'Cowan', '2023-09-08', 'A'),</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -945,15 +945,15 @@
       </c>
       <c r="F15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G15">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79842609388274388</v>
+        <v>1.5071850377472449</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(332, 'Rosetta', 'Schmitt', '2024-03-21', 'A'),</v>
+        <v>(332, 'Rosetta', 'Schmitt', '2024-03-21', 'B'),</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -978,7 +978,7 @@
       </c>
       <c r="G16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.7444041623263622</v>
+        <v>0.70946824612531789</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G17">
         <f t="shared" ca="1" si="1"/>
-        <v>1.4216439578214015</v>
+        <v>1.6254099857555331</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1032,15 +1032,15 @@
       </c>
       <c r="F18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G18">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0481050062932811</v>
+        <v>0.89544757611960613</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(53, 'Deandre', 'Morrison', '2024-06-03', 'B'),</v>
+        <v>(53, 'Deandre', 'Morrison', '2024-06-03', 'A'),</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G19">
         <f t="shared" ca="1" si="1"/>
-        <v>0.18931187584208109</v>
+        <v>0.7683186112633178</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0353176517337772</v>
+        <v>1.7162375658243876</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1119,15 +1119,15 @@
       </c>
       <c r="F21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G21">
         <f t="shared" ca="1" si="1"/>
-        <v>1.4233509627219378</v>
+        <v>0.33636313155452569</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1126, 'Jamison', 'Dalton', '2025-01-08', 'B'),</v>
+        <v>(1126, 'Jamison', 'Dalton', '2025-01-08', 'A'),</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1148,15 +1148,15 @@
       </c>
       <c r="F22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="1"/>
-        <v>1.767697671655762</v>
+        <v>0.19219268907114406</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(481, 'Julius', 'Reyes', '2025-01-16', 'B'),</v>
+        <v>(481, 'Julius', 'Reyes', '2025-01-16', 'A'),</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1177,15 +1177,15 @@
       </c>
       <c r="F23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G23">
         <f t="shared" ca="1" si="1"/>
-        <v>4.8226895886773757E-2</v>
+        <v>1.1939247267494708</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1576, 'Jefferey', 'Byrd', '2025-08-11', 'A'),</v>
+        <v>(1576, 'Jefferey', 'Byrd', '2025-08-11', 'B'),</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1206,15 +1206,15 @@
       </c>
       <c r="F24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="1"/>
-        <v>0.34976889942093004</v>
+        <v>1.9597532795720953</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(756, 'Milton', 'Zimmerman', '2025-12-31', 'A'),</v>
+        <v>(756, 'Milton', 'Zimmerman', '2025-12-31', 'B'),</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1235,15 +1235,15 @@
       </c>
       <c r="F25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0789092469099542</v>
+        <v>0.25714950811369008</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(941, 'Dorthy', 'Watkins', '2026-06-25', 'B'),</v>
+        <v>(941, 'Dorthy', 'Watkins', '2026-06-25', 'A'),</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G26">
         <f t="shared" ca="1" si="1"/>
-        <v>0.6085022698012077</v>
+        <v>0.35641727696860226</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" ca="1" si="2"/>
